--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.83653</v>
+        <v>17.57148</v>
       </c>
       <c r="D2" t="n">
-        <v>17.22207</v>
+        <v>17.33178</v>
       </c>
       <c r="E2" t="n">
-        <v>17.61499</v>
+        <v>17.42648</v>
       </c>
       <c r="F2" t="n">
-        <v>45.67005</v>
+        <v>45.85388</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05392</v>
+        <v>0.05341</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95958</v>
+        <v>1.89326</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.77146</v>
+        <v>17.77502</v>
       </c>
       <c r="D3" t="n">
-        <v>17.61659</v>
+        <v>17.40897</v>
       </c>
       <c r="E3" t="n">
-        <v>17.5543</v>
+        <v>17.45802</v>
       </c>
       <c r="F3" t="n">
-        <v>45.59132</v>
+        <v>44.79008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05537</v>
+        <v>0.05422</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93951</v>
+        <v>1.97755</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.74863</v>
+        <v>17.92666</v>
       </c>
       <c r="D4" t="n">
-        <v>17.33497</v>
+        <v>17.5372</v>
       </c>
       <c r="E4" t="n">
-        <v>17.50009</v>
+        <v>17.7605</v>
       </c>
       <c r="F4" t="n">
-        <v>45.27346</v>
+        <v>45.40683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05246</v>
+        <v>0.05403</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88309</v>
+        <v>1.9558</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.14212</v>
+        <v>17.68867</v>
       </c>
       <c r="D6" t="n">
-        <v>17.27847</v>
+        <v>17.05153</v>
       </c>
       <c r="E6" t="n">
-        <v>17.25856</v>
+        <v>17.18621</v>
       </c>
       <c r="F6" t="n">
-        <v>23.10019</v>
+        <v>23.09749</v>
       </c>
       <c r="G6" t="n">
-        <v>36.11243</v>
+        <v>36.12047</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.65558</v>
+        <v>17.65923</v>
       </c>
       <c r="D7" t="n">
-        <v>16.66676</v>
+        <v>16.7839</v>
       </c>
       <c r="E7" t="n">
-        <v>17.16894</v>
+        <v>17.33828</v>
       </c>
       <c r="F7" t="n">
-        <v>22.55576</v>
+        <v>23.06292</v>
       </c>
       <c r="G7" t="n">
-        <v>36.76059</v>
+        <v>36.19147</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.93565</v>
+        <v>17.56466</v>
       </c>
       <c r="D8" t="n">
-        <v>16.84031</v>
+        <v>16.84444</v>
       </c>
       <c r="E8" t="n">
-        <v>17.68784</v>
+        <v>17.22157</v>
       </c>
       <c r="F8" t="n">
-        <v>23.03736</v>
+        <v>22.97429</v>
       </c>
       <c r="G8" t="n">
-        <v>37.00469</v>
+        <v>36.53107</v>
       </c>
     </row>
   </sheetData>
